--- a/doc/指令.xlsx
+++ b/doc/指令.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Desktop\Frodo_low_overhead\doc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\zzp\project\Frodo_low_overhead\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6A99690-31B5-459F-B79D-B0B0EF8E0109}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9834C2C5-17C4-4A66-ACFC-7383D0E6B71C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="67080" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -525,13 +525,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AD38"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="10.44140625" customWidth="1"/>
-    <col min="20" max="20" width="13.88671875" customWidth="1"/>
+    <col min="1" max="1" width="10.5" customWidth="1"/>
+    <col min="20" max="20" width="13.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -623,7 +623,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -656,7 +656,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -691,7 +691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -741,7 +741,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A5" s="1" t="s">
         <v>29</v>
       </c>
@@ -779,7 +779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A6" s="1" t="s">
         <v>31</v>
       </c>
@@ -811,7 +811,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A7" s="1" t="s">
         <v>11</v>
       </c>
@@ -862,7 +862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
@@ -911,7 +911,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A9" s="1" t="s">
         <v>17</v>
       </c>
@@ -947,7 +947,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A10" s="1" t="s">
         <v>25</v>
       </c>
@@ -993,7 +993,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A11" s="1" t="s">
         <v>28</v>
       </c>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="AC11" s="3"/>
     </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A12" s="1" t="s">
         <v>35</v>
       </c>
@@ -1073,7 +1073,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A19" s="1" t="s">
         <v>1</v>
       </c>
@@ -1100,7 +1100,7 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
     </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A20" s="1" t="s">
         <v>6</v>
       </c>
@@ -1127,7 +1127,7 @@
       <c r="T20" s="3"/>
       <c r="U20" s="3"/>
     </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A21" s="1" t="s">
         <v>10</v>
       </c>
@@ -1154,7 +1154,7 @@
       <c r="T21" s="3"/>
       <c r="U21" s="3"/>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A22" s="1" t="s">
         <v>11</v>
       </c>
@@ -1181,7 +1181,7 @@
       <c r="T22" s="3"/>
       <c r="U22" s="3"/>
     </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A23" s="1" t="s">
         <v>13</v>
       </c>
@@ -1208,7 +1208,7 @@
       <c r="T23" s="3"/>
       <c r="U23" s="3"/>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A24" s="1" t="s">
         <v>17</v>
       </c>
@@ -1235,7 +1235,7 @@
       <c r="T24" s="3"/>
       <c r="U24" s="3"/>
     </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A25" s="1" t="s">
         <v>25</v>
       </c>
@@ -1262,7 +1262,7 @@
       <c r="T25" s="3"/>
       <c r="U25" s="3"/>
     </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A26" s="1" t="s">
         <v>28</v>
       </c>
@@ -1289,7 +1289,7 @@
       <c r="T26" s="3"/>
       <c r="U26" s="3"/>
     </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A27" s="1" t="s">
         <v>29</v>
       </c>
@@ -1316,7 +1316,7 @@
       <c r="T27" s="3"/>
       <c r="U27" s="3"/>
     </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A28" s="1" t="s">
         <v>31</v>
       </c>
@@ -1343,7 +1343,7 @@
       <c r="T28" s="3"/>
       <c r="U28" s="3"/>
     </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A29" s="1" t="s">
         <v>35</v>
       </c>
@@ -1370,7 +1370,7 @@
       <c r="T29" s="3"/>
       <c r="U29" s="3"/>
     </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:21" x14ac:dyDescent="0.15">
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
@@ -1392,7 +1392,7 @@
       <c r="T30" s="3"/>
       <c r="U30" s="3"/>
     </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:21" x14ac:dyDescent="0.15">
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
@@ -1414,7 +1414,7 @@
       <c r="T31" s="3"/>
       <c r="U31" s="3"/>
     </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:21" x14ac:dyDescent="0.15">
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
@@ -1436,7 +1436,7 @@
       <c r="T32" s="3"/>
       <c r="U32" s="3"/>
     </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:21" x14ac:dyDescent="0.15">
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
@@ -1458,7 +1458,7 @@
       <c r="T33" s="3"/>
       <c r="U33" s="3"/>
     </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:21" x14ac:dyDescent="0.15">
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
@@ -1480,7 +1480,7 @@
       <c r="T34" s="3"/>
       <c r="U34" s="3"/>
     </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:21" x14ac:dyDescent="0.15">
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
@@ -1502,7 +1502,7 @@
       <c r="T35" s="3"/>
       <c r="U35" s="3"/>
     </row>
-    <row r="36" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:21" x14ac:dyDescent="0.15">
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
       <c r="D36" s="3"/>
@@ -1524,7 +1524,7 @@
       <c r="T36" s="3"/>
       <c r="U36" s="3"/>
     </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:21" x14ac:dyDescent="0.15">
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
@@ -1546,7 +1546,7 @@
       <c r="T37" s="3"/>
       <c r="U37" s="3"/>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.15">
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
       <c r="D38" s="3"/>
@@ -1570,6 +1570,38 @@
     </row>
   </sheetData>
   <mergeCells count="48">
+    <mergeCell ref="B12:I12"/>
+    <mergeCell ref="J9:S9"/>
+    <mergeCell ref="B10:M10"/>
+    <mergeCell ref="N10:S10"/>
+    <mergeCell ref="B11:M11"/>
+    <mergeCell ref="F9:I9"/>
+    <mergeCell ref="N4:S4"/>
+    <mergeCell ref="N7:S7"/>
+    <mergeCell ref="N8:S8"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="J6:M6"/>
+    <mergeCell ref="B38:U38"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="F3:I3"/>
+    <mergeCell ref="J3:M3"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="J4:M4"/>
+    <mergeCell ref="F4:I4"/>
+    <mergeCell ref="B29:U29"/>
+    <mergeCell ref="B30:U30"/>
+    <mergeCell ref="B31:U31"/>
+    <mergeCell ref="B32:U32"/>
+    <mergeCell ref="B33:U33"/>
+    <mergeCell ref="B34:U34"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="F5:I5"/>
+    <mergeCell ref="J5:M5"/>
+    <mergeCell ref="B26:U26"/>
+    <mergeCell ref="B27:U27"/>
+    <mergeCell ref="B35:U35"/>
+    <mergeCell ref="B36:U36"/>
+    <mergeCell ref="B37:U37"/>
     <mergeCell ref="AB11:AC11"/>
     <mergeCell ref="U8:V8"/>
     <mergeCell ref="B28:U28"/>
@@ -1586,38 +1618,6 @@
     <mergeCell ref="B23:U23"/>
     <mergeCell ref="B24:U24"/>
     <mergeCell ref="B25:U25"/>
-    <mergeCell ref="B26:U26"/>
-    <mergeCell ref="B27:U27"/>
-    <mergeCell ref="B35:U35"/>
-    <mergeCell ref="B36:U36"/>
-    <mergeCell ref="B37:U37"/>
-    <mergeCell ref="B38:U38"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="F3:I3"/>
-    <mergeCell ref="J3:M3"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="J4:M4"/>
-    <mergeCell ref="F4:I4"/>
-    <mergeCell ref="B29:U29"/>
-    <mergeCell ref="B30:U30"/>
-    <mergeCell ref="B31:U31"/>
-    <mergeCell ref="B32:U32"/>
-    <mergeCell ref="B33:U33"/>
-    <mergeCell ref="B34:U34"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="F5:I5"/>
-    <mergeCell ref="J5:M5"/>
-    <mergeCell ref="F9:I9"/>
-    <mergeCell ref="N4:S4"/>
-    <mergeCell ref="N7:S7"/>
-    <mergeCell ref="N8:S8"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="J6:M6"/>
-    <mergeCell ref="B12:I12"/>
-    <mergeCell ref="J9:S9"/>
-    <mergeCell ref="B10:M10"/>
-    <mergeCell ref="N10:S10"/>
-    <mergeCell ref="B11:M11"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1628,7 +1628,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1639,7 +1639,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/doc/指令.xlsx
+++ b/doc/指令.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\zzp\project\Frodo_low_overhead\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9834C2C5-17C4-4A66-ACFC-7383D0E6B71C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3F50BD4-F0D6-4303-84A0-8A7FE18D2779}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="67080" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="42">
   <si>
     <t>指令</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -185,6 +185,10 @@
   </si>
   <si>
     <t>loop[7:6]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ENCDEC</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -625,7 +629,7 @@
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>2</v>
@@ -678,6 +682,9 @@
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
       <c r="M3" s="3"/>
+      <c r="W3" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="X3">
         <v>0</v>
       </c>
@@ -1570,17 +1577,27 @@
     </row>
   </sheetData>
   <mergeCells count="48">
-    <mergeCell ref="B12:I12"/>
-    <mergeCell ref="J9:S9"/>
-    <mergeCell ref="B10:M10"/>
-    <mergeCell ref="N10:S10"/>
-    <mergeCell ref="B11:M11"/>
-    <mergeCell ref="F9:I9"/>
-    <mergeCell ref="N4:S4"/>
-    <mergeCell ref="N7:S7"/>
-    <mergeCell ref="N8:S8"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="J6:M6"/>
+    <mergeCell ref="AB11:AC11"/>
+    <mergeCell ref="U8:V8"/>
+    <mergeCell ref="B28:U28"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="J2:M2"/>
+    <mergeCell ref="B19:U19"/>
+    <mergeCell ref="B20:U20"/>
+    <mergeCell ref="B21:U21"/>
+    <mergeCell ref="B22:U22"/>
+    <mergeCell ref="B7:M7"/>
+    <mergeCell ref="B8:M8"/>
+    <mergeCell ref="U11:V11"/>
+    <mergeCell ref="N11:S11"/>
+    <mergeCell ref="B23:U23"/>
+    <mergeCell ref="B24:U24"/>
+    <mergeCell ref="B25:U25"/>
+    <mergeCell ref="B26:U26"/>
+    <mergeCell ref="B27:U27"/>
+    <mergeCell ref="B35:U35"/>
+    <mergeCell ref="B36:U36"/>
+    <mergeCell ref="B37:U37"/>
     <mergeCell ref="B38:U38"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="F3:I3"/>
@@ -1597,27 +1614,17 @@
     <mergeCell ref="B5:E5"/>
     <mergeCell ref="F5:I5"/>
     <mergeCell ref="J5:M5"/>
-    <mergeCell ref="B26:U26"/>
-    <mergeCell ref="B27:U27"/>
-    <mergeCell ref="B35:U35"/>
-    <mergeCell ref="B36:U36"/>
-    <mergeCell ref="B37:U37"/>
-    <mergeCell ref="AB11:AC11"/>
-    <mergeCell ref="U8:V8"/>
-    <mergeCell ref="B28:U28"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="J2:M2"/>
-    <mergeCell ref="B19:U19"/>
-    <mergeCell ref="B20:U20"/>
-    <mergeCell ref="B21:U21"/>
-    <mergeCell ref="B22:U22"/>
-    <mergeCell ref="B7:M7"/>
-    <mergeCell ref="B8:M8"/>
-    <mergeCell ref="U11:V11"/>
-    <mergeCell ref="N11:S11"/>
-    <mergeCell ref="B23:U23"/>
-    <mergeCell ref="B24:U24"/>
-    <mergeCell ref="B25:U25"/>
+    <mergeCell ref="N4:S4"/>
+    <mergeCell ref="N7:S7"/>
+    <mergeCell ref="N8:S8"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="J6:M6"/>
+    <mergeCell ref="B12:I12"/>
+    <mergeCell ref="J9:S9"/>
+    <mergeCell ref="B10:M10"/>
+    <mergeCell ref="N10:S10"/>
+    <mergeCell ref="B11:M11"/>
+    <mergeCell ref="F9:I9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/doc/指令.xlsx
+++ b/doc/指令.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\zzp\project\Frodo_low_overhead\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3F50BD4-F0D6-4303-84A0-8A7FE18D2779}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7C9CAC2-F6DD-4A8C-86BB-5BA67F60FB4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="67080" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1577,6 +1577,38 @@
     </row>
   </sheetData>
   <mergeCells count="48">
+    <mergeCell ref="B12:I12"/>
+    <mergeCell ref="J9:S9"/>
+    <mergeCell ref="B10:M10"/>
+    <mergeCell ref="N10:S10"/>
+    <mergeCell ref="B11:M11"/>
+    <mergeCell ref="F9:I9"/>
+    <mergeCell ref="N4:S4"/>
+    <mergeCell ref="N7:S7"/>
+    <mergeCell ref="N8:S8"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="J6:M6"/>
+    <mergeCell ref="B38:U38"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="F3:I3"/>
+    <mergeCell ref="J3:M3"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="J4:M4"/>
+    <mergeCell ref="F4:I4"/>
+    <mergeCell ref="B29:U29"/>
+    <mergeCell ref="B30:U30"/>
+    <mergeCell ref="B31:U31"/>
+    <mergeCell ref="B32:U32"/>
+    <mergeCell ref="B33:U33"/>
+    <mergeCell ref="B34:U34"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="F5:I5"/>
+    <mergeCell ref="J5:M5"/>
+    <mergeCell ref="B26:U26"/>
+    <mergeCell ref="B27:U27"/>
+    <mergeCell ref="B35:U35"/>
+    <mergeCell ref="B36:U36"/>
+    <mergeCell ref="B37:U37"/>
     <mergeCell ref="AB11:AC11"/>
     <mergeCell ref="U8:V8"/>
     <mergeCell ref="B28:U28"/>
@@ -1593,38 +1625,6 @@
     <mergeCell ref="B23:U23"/>
     <mergeCell ref="B24:U24"/>
     <mergeCell ref="B25:U25"/>
-    <mergeCell ref="B26:U26"/>
-    <mergeCell ref="B27:U27"/>
-    <mergeCell ref="B35:U35"/>
-    <mergeCell ref="B36:U36"/>
-    <mergeCell ref="B37:U37"/>
-    <mergeCell ref="B38:U38"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="F3:I3"/>
-    <mergeCell ref="J3:M3"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="J4:M4"/>
-    <mergeCell ref="F4:I4"/>
-    <mergeCell ref="B29:U29"/>
-    <mergeCell ref="B30:U30"/>
-    <mergeCell ref="B31:U31"/>
-    <mergeCell ref="B32:U32"/>
-    <mergeCell ref="B33:U33"/>
-    <mergeCell ref="B34:U34"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="F5:I5"/>
-    <mergeCell ref="J5:M5"/>
-    <mergeCell ref="N4:S4"/>
-    <mergeCell ref="N7:S7"/>
-    <mergeCell ref="N8:S8"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="J6:M6"/>
-    <mergeCell ref="B12:I12"/>
-    <mergeCell ref="J9:S9"/>
-    <mergeCell ref="B10:M10"/>
-    <mergeCell ref="N10:S10"/>
-    <mergeCell ref="B11:M11"/>
-    <mergeCell ref="F9:I9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
